--- a/docs/AgileProcess_6팀.xlsx
+++ b/docs/AgileProcess_6팀.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\whale-project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\whale-project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3EAF76-DC89-4C7B-8D56-8C64ABC9CFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC69958-0CC5-493C-A50E-8BE7C0FCC605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Process Definition" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="74">
   <si>
     <t xml:space="preserve">Backlog NO. </t>
   </si>
@@ -84,227 +84,6 @@
   </si>
   <si>
     <t>홈페이지 보기</t>
-  </si>
-  <si>
-    <t>로그인/회원가입</t>
-  </si>
-  <si>
-    <t>1. 백로그 4번 실행
-2. 화면 오른쪽 위 "회원가입" 버튼을 클릭한다
-3. 아이디(3자 이상), 이메일, 비밀번호(6자 이상)를 입력하고 "가입하기"를 클릭한다
-4. 가입 완료 후 자동으로 로그인되며 오른쪽 위에 아이디가 표시된다
-5. 아이디를 클릭하면 회원정보 페이지(아이디/이메일/가입일)로 이동한다
-6. 로그아웃 후 "로그인" 버튼을 클릭하여 다시 로그인한다</t>
-  </si>
-  <si>
-    <t>차트 변환</t>
-  </si>
-  <si>
-    <t>1. 백로그 4번을 실행한다 
-2. 기본값인 라인 차트가 표시된다
-3. [캔들스틱] 버튼을 클릭한다
-4. 차트가 캔들스틱 형태로 전환된다
-5. 차트 위에 마우스를 올리면 시가/고가/저가/종가가 툴팁으로 표시된다
-6. 다시 [라인] 버튼을 클릭하면 기존 라인 차트로 돌아온다</t>
-  </si>
-  <si>
-    <t>특정 고래 거래 상세 조회</t>
-  </si>
-  <si>
-    <t>1. 백로그 4번 실행
-2. 실시간 고래 활동 로그에서 특정 거래 행을 클릭한다
-3. 팝업이 열리며 해당 거래 이후 1분/5분 뒤 실제 가격 변화가 표시된다
-4. 매수 거래라면 이후 상승/하락 여부, 등락률이 함께 표시된다</t>
-  </si>
-  <si>
-    <t>시간대별 고래 활동 통계</t>
-  </si>
-  <si>
-    <t>1. index.html 더블 클릭
-2. 시간대별 고래 활동 통계 섹션을 확인한다
-3. 오늘 0시~23시 중 고래 거래가 많았던 시간대가 바 차트로 표시된다
-4. 특정 시간대 바를 클릭하면 해당 시간의 고래 거래 건수와 총액이 표시된다</t>
-  </si>
-  <si>
-    <t>예정</t>
-  </si>
-  <si>
-    <t>날짜별 고래 히스토리 조회</t>
-  </si>
-  <si>
-    <t>1. index.html 더블 클릭
-2. 날짜 선택 달력에서 과거 날짜를 선택한다
-3. 선택한 날짜의 고래 활동 로그가 표시된다
-4. 해당 날짜의 고래 거래 건수, 총 매수/매도액이 함께 표시된다</t>
-  </si>
-  <si>
-    <t>가격 예측 피처 엔지니어링</t>
-  </si>
-  <si>
-    <t>1. analyzer/feature_engineering.py 파일을 실행한다
-2. 고래 거래 발생 시점 기준 이전 10분간 가격 변동률, 매수/매도 비율, 거래량 변화율 등 피처를 추출한다
-3. 고래 거래 후 1분/5분/30분 뒤 가격 변화율을 레이블(상승/하락)로 생성한다
-4. 피처와 레이블이 포함된 CSV 또는 DB 테이블이 출력된다</t>
-  </si>
-  <si>
-    <t>가격 방향 예측 모델 학습</t>
-  </si>
-  <si>
-    <t>1. analyzer/feature_engineering.py 에서 생성된 피처 데이터를 불러온다
-2. 베이스 스크립트(analyzer/train_model.py)를 실행한다
-3. XGBoost 또는 RandomForest로 고래 거래 후 가격 상승/하락 분류 모델이 학습되고 model.pkl 파일로 저장된다
-4. 1분/5분/30분 각 예측 구간별 정확도(Accuracy), 정밀도(Precision), 재현율(Recall) 지표가 출력된다</t>
-  </si>
-  <si>
-    <t>가격 예측 API</t>
-  </si>
-  <si>
-    <t>1. backend/server.py 파일을 실행한다
-2. 브라우저 또는 터미널에서 GET /predict/price-after-whale 엔드포인트를 호출한다
-3. 최근 고래 거래 데이터를 기반으로 1분/5분/30분 후 가격 방향 예측(상승/하락/유지)이 JSON으로 반환된다
-4. 응답 예시: {1m: {direction: UP, confidence: 78.3}, 5m: {direction: DOWN, confidence: 61.2}, 30m: {direction: UP, confidence: 55.0}}</t>
-  </si>
-  <si>
-    <t>가격 예측 대시보드 연동</t>
-  </si>
-  <si>
-    <t>1. index.html 파일을 클릭한다
-2. 실시간 고래 활동 로그에서 고래 거래 행을 클릭하여 상세 모달을 연다
-3. 모달 하단에 AI 가격 예측 영역이 표시된다
-4. 1분/5분/30분 후 예측 방향(▲상승/▼하락), 신뢰도(HIGH/MED/LOW) 및 예측 근거(매수 강도, 거래량 이상치)가 함께 표시된다
-5. 5분마다 자동 업데이트되어 최신 예측 결과로 갱신된다</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Sprint No.</t>
-  </si>
-  <si>
-    <t>Backlog No.</t>
-  </si>
-  <si>
-    <t>1,2,3</t>
-  </si>
-  <si>
-    <t>5,6,7</t>
-  </si>
-  <si>
-    <t>8,9</t>
-  </si>
-  <si>
-    <t>10,11</t>
-  </si>
-  <si>
-    <t>12,13</t>
-  </si>
-  <si>
-    <t>13,14</t>
-  </si>
-  <si>
-    <t>15,16</t>
-  </si>
-  <si>
-    <t>17,18</t>
-  </si>
-  <si>
-    <t>19,20,26,27</t>
-  </si>
-  <si>
-    <t>21,22,28</t>
-  </si>
-  <si>
-    <t>Minor MileStone</t>
-  </si>
-  <si>
-    <t>업비트-Kafka-DB 파이프라인 구축 및 데이터 중복 방지 로직 적용</t>
-  </si>
-  <si>
-    <t>FastAPI 및 WebSocket 기반의 실시간 가상화폐 대량 거래 탐지 및 시각화 시스템 구현</t>
-  </si>
-  <si>
-    <t>차트 고도화(캔들/라인 전환) 및 고래 거래 상세 분석 기능 구현</t>
-  </si>
-  <si>
-    <t>시간대별 고래 활동 통계 및 히스토리 조회 기능 구현</t>
-  </si>
-  <si>
-    <t>피처 엔지니어링 및 고래 거래 후 가격 방향 예측 모델 학습/평가 완료</t>
-  </si>
-  <si>
-    <t>고래 거래 후 가격 방향 예측 API 개발 및 대시보드 연동 완료</t>
-  </si>
-  <si>
-    <t>Query Service 기본 구조 및 고래 거래 조회 API</t>
-  </si>
-  <si>
-    <t>해석 요약 지표 조회 API 및 마켓별 필터 기능</t>
-  </si>
-  <si>
-    <t>서비스 분리 및 Docker Compose 통합 실행</t>
-  </si>
-  <si>
-    <t>CQRS 구조 정리 및 테스트 코드 작성</t>
-  </si>
-  <si>
-    <t>AI 모델 학습 및 Prediction Service 통합 테스트</t>
-  </si>
-  <si>
-    <t>Major MileStone</t>
-  </si>
-  <si>
-    <t>실시간 고래 탐지 인프라 구축 및 대시보드 기능 고도화 완료</t>
-  </si>
-  <si>
-    <t>고래 거래 이후 가격 방향 예측 모델 구축 및 대시보드 연동 완료</t>
-  </si>
-  <si>
-    <t>AI 예측 모델링 및 최종 최적화/검증</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprint No. </t>
-  </si>
-  <si>
-    <t>BackLog</t>
-  </si>
-  <si>
-    <t>개발 리더(발표자)</t>
-  </si>
-  <si>
-    <t>개발자 2</t>
-  </si>
-  <si>
-    <t>개발자 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">결과 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">완료 </t>
-  </si>
-  <si>
-    <t>Release Burndown</t>
-  </si>
-  <si>
-    <t>Only edit shaded columns, others are calculated</t>
-  </si>
-  <si>
-    <t>Week</t>
-  </si>
-  <si>
-    <t>Backlog</t>
-  </si>
-  <si>
-    <t>Percent Complete</t>
-  </si>
-  <si>
-    <t>Remaining</t>
-  </si>
-  <si>
-    <t>Done</t>
-  </si>
-  <si>
-    <t>variation</t>
   </si>
   <si>
     <t xml:space="preserve">1. 로컬에 있는 whale-project 폴더 열기 
@@ -315,7 +94,217 @@
 7. index.html 더블 클릭
 8. 연결을 기다리면 화면(코인 선택 드롭다운, 표시 화폐 전환 버튼(KRW/USD), 실시간 환율, 고래 기준 슬라이더, 실시간 가격(기준가 대비/등락률), 24H 고래 매수액(누적/건수), 고래 매수 강도(변동률), 타임프레임 선택 버튼(1초/1분/30분/1시간), 실시간 차트, 실시간 고래 활동 로그(시간·구분·가격·수량·총액), 더보기 버튼, 실시간 연결 상태 표시)이 출력됨 
 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로그인/회원가입</t>
+  </si>
+  <si>
+    <t>1. 백로그 4번 실행
+2. 화면 오른쪽 위 "회원가입" 버튼을 클릭한다
+3. 아이디(3자 이상), 이메일, 비밀번호(6자 이상)를 입력하고 "가입하기"를 클릭한다
+4. 가입 완료 후 자동으로 로그인되며 오른쪽 위에 아이디가 표시된다
+5. 아이디를 클릭하면 회원정보 페이지(아이디/이메일/가입일)로 이동한다
+6. 로그아웃 후 "로그인" 버튼을 클릭하여 다시 로그인한다</t>
+  </si>
+  <si>
+    <t>차트 변환</t>
+  </si>
+  <si>
+    <t>1. 백로그 4번을 실행한다 
+2. 기본값인 라인 차트가 표시된다
+3. [캔들스틱] 버튼을 클릭한다
+4. 차트가 캔들스틱 형태로 전환된다
+5. 차트 위에 마우스를 올리면 시가/고가/저가/종가가 툴팁으로 표시된다
+6. 다시 [라인] 버튼을 클릭하면 기존 라인 차트로 돌아온다</t>
+  </si>
+  <si>
+    <t>특정 고래 거래 상세 조회</t>
+  </si>
+  <si>
+    <t>1. 백로그 4번 실행
+2. 실시간 고래 활동 로그에서 특정 거래 행을 클릭한다
+3. 팝업이 열리며 해당 거래 이후 1분/5분 뒤 실제 가격 변화가 표시된다
+4. 매수 거래라면 이후 상승/하락 여부, 등락률이 함께 표시된다</t>
+  </si>
+  <si>
+    <t>시간대별 고래 활동 통계</t>
+  </si>
+  <si>
+    <t>1. index.html 더블 클릭
+2. 시간대별 고래 활동 통계 섹션을 확인한다
+3. 오늘 0시~23시 중 고래 거래가 많았던 시간대가 바 차트로 표시된다
+4. 특정 시간대 바를 클릭하면 해당 시간의 고래 거래 건수와 총액이 표시된다</t>
+  </si>
+  <si>
+    <t>날짜별 고래 히스토리 조회</t>
+  </si>
+  <si>
+    <t>1. index.html 더블 클릭
+2. 날짜 선택 달력에서 과거 날짜를 선택한다
+3. 선택한 날짜의 고래 활동 로그가 표시된다
+4. 해당 날짜의 고래 거래 건수, 총 매수/매도액이 함께 표시된다</t>
+  </si>
+  <si>
+    <t>가격 예측 대시보드 연동</t>
+  </si>
+  <si>
+    <t>1. index.html 파일을 클릭한다
+2. 실시간 고래 활동 로그에서 고래 거래 행을 클릭하여 상세 모달을 연다
+3. 모달 하단에 AI 가격 예측 영역이 표시된다
+4. 1분/5분/30분 후 예측 방향(▲상승/▼하락), 신뢰도(HIGH/MED/LOW) 및 예측 근거(매수 강도, 거래량 이상치)가 함께 표시된다
+5. 5분마다 자동 업데이트되어 최신 예측 결과로 갱신된다</t>
+  </si>
+  <si>
+    <t>예정</t>
+  </si>
+  <si>
+    <t>슬랙 알림</t>
+  </si>
+  <si>
+    <t>유저별 웹훅 등록 및 고래 감지 알림 전송</t>
+  </si>
+  <si>
+    <t>1. 로그인 후 프로필 페이지로 이동한다
+2. 슬랙 웹훅 URL 입력란에 본인의 슬랙 채널 웹훅 URL을 입력하고 저장 버튼을 클릭한다
+3. 고래 거래(1억 원 이상) 발생 시 등록된 슬랙 채널에 알림이 자동으로 전송된다
+4. 슬랙 메시지에 코인명, 거래금액, 매수/매도 방향, AI 예측 결과(1분/5분/30분 방향 및 신뢰도)가 카드 형태로 표시된다
+5. 웹훅 URL을 삭제하면 알림 전송이 중단된다</t>
+  </si>
+  <si>
+    <t>미완</t>
+  </si>
+  <si>
+    <t>백테스팅</t>
+  </si>
+  <si>
+    <t>AI 예측 수익률 시뮬레이션</t>
+  </si>
+  <si>
+    <t>1. index.html을 열고 상단 메뉴에서 [백테스팅] 탭을 클릭한다
+2. BTC/ETH 코인을 선택하고 타임프레임(1분/5분/30분)을 선택한다
+3. AI 예측 신호를 따랐을 경우의 누적 수익률 곡선이 차트로 표시된다
+4. 승률, 총 거래 횟수, 최대 손실폭(MDD), 누적 수익률 수치가 카드 형태로 상단에 표시된다
+5. 만약 1,000,000원으로 시작했다면 현재 얼마인지 시뮬레이션 결과가 표시된다</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Sprint No.</t>
+  </si>
+  <si>
+    <t>Backlog No.</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>5,6,7</t>
+  </si>
+  <si>
+    <t>8,9</t>
+  </si>
+  <si>
+    <t>17,18</t>
+  </si>
+  <si>
+    <t>19,20,26,27</t>
+  </si>
+  <si>
+    <t>21,22,28</t>
+  </si>
+  <si>
+    <t>Minor MileStone</t>
+  </si>
+  <si>
+    <t>업비트-Kafka-DB 파이프라인 구축 및 데이터 중복 방지 로직 적용</t>
+  </si>
+  <si>
+    <t>FastAPI 및 WebSocket 기반의 실시간 가상화폐 대량 거래 탐지 및 시각화 시스템 구현</t>
+  </si>
+  <si>
+    <t>차트 고도화(캔들/라인 전환) 및 고래 거래 상세 분석 기능 구현</t>
+  </si>
+  <si>
+    <t>시간대별 고래 활동 통계 및 히스토리 조회 기능 구현</t>
+  </si>
+  <si>
+    <t>피처 엔지니어링 및 고래 거래 후 가격 방향 예측 모델 학습/평가 완료</t>
+  </si>
+  <si>
+    <t>고래 거래 후 가격 방향 예측 API 개발 및 대시보드 연동 완료</t>
+  </si>
+  <si>
+    <t>슬랙 알림 연동 - 유저별 웹훅 등록 및 고래 감지 시 AI 예측 포함 알림 전송 완료</t>
+  </si>
+  <si>
+    <t>백테스팅 대시보드 - AI 예측 수익률 시뮬레이션 및 승률 시각화 완료</t>
+  </si>
+  <si>
+    <t>서비스 분리 및 Docker Compose 통합 실행</t>
+  </si>
+  <si>
+    <t>CQRS 구조 정리 및 테스트 코드 작성</t>
+  </si>
+  <si>
+    <t>AI 모델 학습 및 Prediction Service 통합 테스트</t>
+  </si>
+  <si>
+    <t>Major MileStone</t>
+  </si>
+  <si>
+    <t>실시간 고래 탐지 인프라 구축 및 대시보드 기능 고도화 완료</t>
+  </si>
+  <si>
+    <t>고래 거래 이후 가격 방향 예측 모델 구축 및 대시보드 연동 완료</t>
+  </si>
+  <si>
+    <t>AI 예측 모델 백테스팅 완료 및 성능 검증</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint No. </t>
+  </si>
+  <si>
+    <t>BackLog</t>
+  </si>
+  <si>
+    <t>개발 리더(발표자)</t>
+  </si>
+  <si>
+    <t>개발자 2</t>
+  </si>
+  <si>
+    <t>개발자 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">결과 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">완료 </t>
+  </si>
+  <si>
+    <t>Release Burndown</t>
+  </si>
+  <si>
+    <t>Only edit shaded columns, others are calculated</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>Percent Complete</t>
+  </si>
+  <si>
+    <t>Remaining</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>variation</t>
   </si>
 </sst>
 </file>
@@ -782,7 +771,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -888,16 +877,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1073,7 +1063,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7668-49F0-AE4C-C09122605BDF}"/>
+              <c16:uniqueId val="{00000000-2E26-4696-8BA0-9203E62B866B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1591,7 +1581,7 @@
     <row r="1" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="2" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B2" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" s="28">
         <v>46107</v>
@@ -1629,7 +1619,7 @@
     </row>
     <row r="3" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="26">
         <v>1</v>
@@ -1668,111 +1658,111 @@
     </row>
     <row r="4" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B4" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="21">
         <v>4</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="H4" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="21" t="s">
+      <c r="G4" s="20">
+        <v>10</v>
+      </c>
+      <c r="H4" s="21">
+        <v>10</v>
+      </c>
+      <c r="I4" s="21">
+        <v>11</v>
+      </c>
+      <c r="J4" s="23">
+        <v>12</v>
+      </c>
+      <c r="K4" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="J4" s="23" t="s">
+      <c r="L4" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="25" t="s">
+      <c r="M4" s="32" t="s">
         <v>42</v>
-      </c>
-      <c r="L4" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>44</v>
       </c>
       <c r="N4"/>
     </row>
     <row r="5" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="E5" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="F5" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="G5" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="H5" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="I5" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="J5" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="17" t="s">
+      <c r="K5" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="L5" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="17" t="s">
+      <c r="M5" s="32" t="s">
         <v>54</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="M5" s="32" t="s">
-        <v>56</v>
       </c>
       <c r="N5" s="37"/>
     </row>
     <row r="6" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="H6" s="41"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
       <c r="O6" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="G6:I6"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="J6:N6"/>
+    <mergeCell ref="G6:H6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1781,7 +1771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10.8984375" style="38" customWidth="1"/>
@@ -1808,7 +1798,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1850,7 +1840,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="208.8" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1859,21 +1849,21 @@
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="6" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="E5" s="34" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="104.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="7.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="35" t="s">
         <v>7</v>
@@ -1887,10 +1877,10 @@
         <v>12</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="34" t="s">
         <v>7</v>
@@ -1904,10 +1894,10 @@
         <v>12</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="34" t="s">
         <v>7</v>
@@ -1918,14 +1908,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="104.4" customHeight="1" x14ac:dyDescent="0.4">
@@ -1940,7 +1930,7 @@
         <v>23</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.4">
@@ -1954,66 +1944,65 @@
         <v>25</v>
       </c>
       <c r="E11" s="35" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>26</v>
+      <c r="B12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>21</v>
+        <v>29</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
-        <v>28</v>
+      <c r="B13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="35" t="s">
-        <v>21</v>
+        <v>33</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="87" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="34"/>
+    </row>
+    <row r="15" spans="1:5" ht="104.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="34"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" ht="104.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="34"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:5" ht="104.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -2123,105 +2112,78 @@
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
-      <c r="E32" s="34"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="34"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
-      <c r="E34" s="34"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A36" s="24"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
       <c r="D41" s="6"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
       <c r="D43" s="6"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
       <c r="D44" s="6"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="A48"/>
-      <c r="B48"/>
-      <c r="D48"/>
-      <c r="E48"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2243,26 +2205,26 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>66</v>
-      </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B3" s="44">
+      <c r="B3" s="45">
         <v>1</v>
       </c>
       <c r="C3" s="1">
@@ -2272,11 +2234,11 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B4" s="45"/>
+      <c r="B4" s="46"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
@@ -2284,7 +2246,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2306,48 +2268,48 @@
     <col min="3" max="3" width="9.5" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.09765625" style="9" customWidth="1"/>
     <col min="5" max="5" width="11.09765625" style="9" customWidth="1"/>
-    <col min="6" max="12" width="8.8984375" style="9" customWidth="1"/>
-    <col min="13" max="16384" width="8.8984375" style="9"/>
+    <col min="6" max="14" width="8.8984375" style="9" customWidth="1"/>
+    <col min="15" max="16384" width="8.8984375" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="49" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="B4" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="51" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="50"/>
+      <c r="B5" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="50" t="s">
+      <c r="C5" s="11" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49"/>
-      <c r="B5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="49"/>
+      <c r="E5" s="50"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="12">

--- a/docs/AgileProcess_6팀.xlsx
+++ b/docs/AgileProcess_6팀.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\whale-project\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D0BD299-301E-44B0-AB1B-571BC491DB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC58277D-6F20-4DB3-8C62-9C994264674B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Process Definition" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="83">
   <si>
     <t xml:space="preserve">Backlog NO. </t>
   </si>
@@ -269,15 +269,6 @@
     <t>12,13,14</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>Minor MileStone</t>
   </si>
   <si>
@@ -303,12 +294,6 @@
   </si>
   <si>
     <t>공포&amp;탐욕 지수, 비트코인 도미넌스, 김치 프리미엄 외부 지표 3개 연동 완료 (5분 캐싱, 거래소 페이지 하단 카드 영역 배치)</t>
-  </si>
-  <si>
-    <t>백테스팅 기본 기능 구현 (예측 모델 선택 버튼, 성과 카드 4개, AI 신호 누적수익률 차트 + BTC 시장 흐름 참고선)</t>
-  </si>
-  <si>
-    <t>백테스팅 고도화 (날짜 범위 선택, BTC/ETH 비교 탭, 100만원 시뮬레이션 카드, 거래 상세 목록 테이블)</t>
   </si>
   <si>
     <t>AI 예측현황 탭 완성 (예측 모델별 정확도 카드 3개, 시간대별 정확도 바 차트, 최근 예측 결과 목록 30건)</t>
@@ -381,6 +366,18 @@
    - 최종 평가금액: 복리 계산 결과 (고래 신호마다 전액 투입)
 6. 거래 상세 목록 테이블이 표시된다
    - 컬럼: 진입 시각 / 청산 시각 / 포지션(매수/매도) / 진입가 / 청산가 / 수익률 / 결과(적중/오류)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15,16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백테스팅 기능 구현 (예측 모델 선택 버튼, 성과 카드 4개, AI 신호 누적수익률 차트 + BTC 시장 흐름 참고선, 날짜 범위 선택, BTC/ETH 비교 탭, 100만원 시뮬레이션 카드, 거래 상세 목록 테이블)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발표준비</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -464,7 +461,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,8 +497,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -816,27 +819,42 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="thin">
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -854,7 +872,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -956,25 +974,29 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="20" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1652,19 +1674,19 @@
   <dimension ref="B1:O6"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="15.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.8984375" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="75.8984375" style="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55.3984375" style="38" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47" style="38" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.3984375" style="38" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="53.796875" style="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="70.5" style="38" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="73.09765625" style="38" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="64.19921875" style="38" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="69.09765625" style="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="64.3984375" style="38" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.8984375" style="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.8984375" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75.8984375" style="37" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.3984375" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47" style="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.3984375" style="37" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="53.796875" style="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="70.5" style="37" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="73.09765625" style="37" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="181" style="37" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="69.09765625" style="37" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="64.3984375" style="37" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.8984375" style="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
@@ -1697,7 +1719,7 @@
         <v>46156</v>
       </c>
       <c r="K2" s="28">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="L2" s="28">
         <v>46170</v>
@@ -1774,84 +1796,81 @@
         <v>49</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>50</v>
-      </c>
-      <c r="L4" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" s="32" t="s">
-        <v>52</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="L4" s="23">
+        <v>17</v>
+      </c>
+      <c r="M4" s="32"/>
       <c r="N4"/>
     </row>
     <row r="5" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="F5" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="G5" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="H5" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="I5" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="J5" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="K5" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="L5" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="I5" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="J5" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="M5" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" s="37"/>
+      <c r="M5" s="38"/>
+      <c r="N5"/>
     </row>
     <row r="6" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B6" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="41"/>
+        <v>60</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="42"/>
       <c r="G6" s="43" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="41"/>
-      <c r="J6" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
+        <v>62</v>
+      </c>
+      <c r="H6" s="41"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="44" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="39" t="s">
+        <v>82</v>
+      </c>
       <c r="O6" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C6:F6"/>
-    <mergeCell ref="J6:N6"/>
     <mergeCell ref="G6:I6"/>
+    <mergeCell ref="J6:L6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1863,10 +1882,10 @@
   <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.8984375" style="38" customWidth="1"/>
-    <col min="2" max="2" width="17.796875" style="38" customWidth="1"/>
-    <col min="3" max="3" width="17.59765625" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="72.8984375" style="38" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.8984375" style="37" customWidth="1"/>
+    <col min="2" max="2" width="17.796875" style="37" customWidth="1"/>
+    <col min="3" max="3" width="17.59765625" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="72.8984375" style="37" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.796875" style="35" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2066,8 +2085,8 @@
       <c r="D13" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="35" t="s">
-        <v>31</v>
+      <c r="E13" s="34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="121.8" x14ac:dyDescent="0.4">
@@ -2083,8 +2102,8 @@
       <c r="D14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="35" t="s">
-        <v>31</v>
+      <c r="E14" s="34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="139.19999999999999" x14ac:dyDescent="0.4">
@@ -2100,8 +2119,8 @@
       <c r="D15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="35" t="s">
-        <v>31</v>
+      <c r="E15" s="34" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="261" x14ac:dyDescent="0.4">
@@ -2132,7 +2151,7 @@
         <v>39</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E17" s="35" t="s">
         <v>31</v>
@@ -2363,35 +2382,35 @@
   <dimension ref="B2:G4"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="10.19921875" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.3984375" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.09765625" style="38" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="38" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="38" customWidth="1"/>
+    <col min="2" max="2" width="10.19921875" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.3984375" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.09765625" style="37" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="37" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="37" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B3" s="44">
+      <c r="B3" s="46">
         <v>1</v>
       </c>
       <c r="C3" s="1">
@@ -2401,11 +2420,11 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.4">
-      <c r="B4" s="45"/>
+      <c r="B4" s="47"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
@@ -2413,7 +2432,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2441,42 +2460,42 @@
   <sheetData>
     <row r="1" spans="1:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="48" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="52" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="51"/>
+      <c r="B5" s="11" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="C5" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48" t="s">
+      <c r="D5" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="50" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="13.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49"/>
-      <c r="B5" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E5" s="49"/>
+      <c r="E5" s="51"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
